--- a/VerveStacks_TUR_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_TUR_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_TUR_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A567003-8383-4308-BC0C-9598CF003122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{973232F4-B06C-4ED9-B01D-478175E652E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="11422" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="12772" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -836,18 +836,168 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_TUR_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_TUR_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_TUR_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_TUR_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_TUR_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_TUR_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_TUR_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_TUR_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_TUR_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_TUR_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_TUR_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_TUR_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_TUR_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_TUR_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_TUR_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_TUR_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_TUR_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_TUR_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_TUR_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_TUR_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_TUR_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_TUR_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_TUR_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_TUR_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_TUR_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_TUR_006</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 6</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_TUR_007</t>
   </si>
   <si>
@@ -866,46 +1016,28 @@
     <t>connecting solar to buses in cluster 29</t>
   </si>
   <si>
-    <t>distr_solelc_spv_TUR_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_TUR_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_TUR_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_TUR_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_TUR_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_TUR_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_TUR_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
+    <t>distr_solelc_spv_TUR_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_TUR_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_TUR_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_TUR_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
   </si>
   <si>
     <t>distr_solelc_spv_TUR_014</t>
@@ -914,147 +1046,84 @@
     <t>connecting solar to buses in cluster 14</t>
   </si>
   <si>
-    <t>distr_solelc_spv_TUR_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_TUR_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_TUR_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_TUR_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_TUR_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_TUR_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_TUR_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_TUR_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_TUR_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_TUR_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_TUR_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_TUR_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_TUR_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_TUR_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_TUR_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_TUR_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_TUR_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_TUR_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_TUR_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_TUR_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_TUR_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_TUR_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_Zonguldak_TUR</t>
+  </si>
+  <si>
+    <t>e_Antalya_TUR</t>
+  </si>
+  <si>
+    <t>e_Etimesgut_TUR</t>
+  </si>
+  <si>
+    <t>e_Osmaniye_TUR</t>
+  </si>
+  <si>
+    <t>e_Agr_TUR</t>
+  </si>
+  <si>
+    <t>e_Adyaman_TUR</t>
+  </si>
+  <si>
+    <t>e_Ordu_TUR</t>
+  </si>
+  <si>
+    <t>e_Cermik_TUR</t>
+  </si>
+  <si>
+    <t>e_Istanbul_TUR</t>
+  </si>
+  <si>
+    <t>e_Beysehir_TUR</t>
+  </si>
+  <si>
+    <t>e_Hatay_TUR</t>
+  </si>
+  <si>
+    <t>e_Arapgir_TUR</t>
+  </si>
+  <si>
     <t>e_Diyarbakr_TUR</t>
   </si>
   <si>
+    <t>e_Amasya_TUR</t>
+  </si>
+  <si>
+    <t>e_Konya_TUR</t>
+  </si>
+  <si>
+    <t>e_Akhisar_TUR</t>
+  </si>
+  <si>
+    <t>e_Canakkale_TUR</t>
+  </si>
+  <si>
+    <t>e_Artvin_TUR</t>
+  </si>
+  <si>
+    <t>e_Kocaeli_TUR</t>
+  </si>
+  <si>
+    <t>e_Duzce_TUR</t>
+  </si>
+  <si>
+    <t>e_Elbistan_TUR</t>
+  </si>
+  <si>
+    <t>e_Denizli_TUR</t>
+  </si>
+  <si>
+    <t>e_Milas_TUR</t>
+  </si>
+  <si>
+    <t>e_Sakarya_TUR</t>
+  </si>
+  <si>
     <t>e_Izmir_TUR</t>
   </si>
   <si>
@@ -1064,85 +1133,70 @@
     <t>e_Siirt_TUR</t>
   </si>
   <si>
-    <t>e_Zonguldak_TUR</t>
-  </si>
-  <si>
-    <t>e_Antalya_TUR</t>
-  </si>
-  <si>
-    <t>e_Amasya_TUR</t>
-  </si>
-  <si>
-    <t>e_Konya_TUR</t>
-  </si>
-  <si>
-    <t>e_Cermik_TUR</t>
-  </si>
-  <si>
-    <t>e_Istanbul_TUR</t>
+    <t>e_Afyonkarahisar_TUR</t>
+  </si>
+  <si>
+    <t>e_Erzurum_TUR</t>
+  </si>
+  <si>
+    <t>e_Esenyurt_TUR</t>
   </si>
   <si>
     <t>e_Corlu_TUR</t>
   </si>
   <si>
-    <t>e_Kocaeli_TUR</t>
-  </si>
-  <si>
-    <t>e_Duzce_TUR</t>
-  </si>
-  <si>
-    <t>e_Esenyurt_TUR</t>
-  </si>
-  <si>
-    <t>e_Etimesgut_TUR</t>
-  </si>
-  <si>
-    <t>e_Osmaniye_TUR</t>
-  </si>
-  <si>
-    <t>e_Agr_TUR</t>
-  </si>
-  <si>
-    <t>e_Adyaman_TUR</t>
-  </si>
-  <si>
-    <t>e_Ordu_TUR</t>
-  </si>
-  <si>
-    <t>e_Elbistan_TUR</t>
-  </si>
-  <si>
-    <t>e_Milas_TUR</t>
-  </si>
-  <si>
-    <t>e_Sakarya_TUR</t>
-  </si>
-  <si>
-    <t>e_Akhisar_TUR</t>
-  </si>
-  <si>
-    <t>e_Canakkale_TUR</t>
-  </si>
-  <si>
-    <t>e_Artvin_TUR</t>
-  </si>
-  <si>
-    <t>e_Afyonkarahisar_TUR</t>
-  </si>
-  <si>
-    <t>e_Erzurum_TUR</t>
-  </si>
-  <si>
-    <t>e_Denizli_TUR</t>
-  </si>
-  <si>
-    <t>e_Beysehir_TUR</t>
-  </si>
-  <si>
-    <t>e_Hatay_TUR</t>
-  </si>
-  <si>
-    <t>e_Arapgir_TUR</t>
+    <t>distr_wonelc_won_TUR_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_TUR_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_TUR_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_TUR_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_TUR_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_TUR_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_TUR_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_TUR_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_TUR_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
   </si>
   <si>
     <t>distr_wonelc_won_TUR_005</t>
@@ -1175,30 +1229,60 @@
     <t>connecting wind onshore to buses in cluster 27</t>
   </si>
   <si>
+    <t>distr_wonelc_won_TUR_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_TUR_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_TUR_009</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 9</t>
   </si>
   <si>
+    <t>distr_wonelc_won_TUR_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_TUR_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_TUR_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_TUR_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_TUR_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_TUR_025</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 25</t>
   </si>
   <si>
-    <t>distr_wonelc_won_TUR_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_TUR_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_TUR_015</t>
   </si>
   <si>
@@ -1217,94 +1301,37 @@
     <t>connecting wind onshore to buses in cluster 19</t>
   </si>
   <si>
-    <t>distr_wonelc_won_TUR_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_TUR_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_TUR_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_TUR_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_TUR_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_TUR_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_TUR_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_TUR_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_TUR_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_TUR_020</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 20</t>
   </si>
   <si>
-    <t>distr_wonelc_won_TUR_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_TUR_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_TUR_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_TUR_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_TUR_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
+    <t>elc_won_TUR_001</t>
+  </si>
+  <si>
+    <t>elc_won_TUR_003</t>
+  </si>
+  <si>
+    <t>elc_won_TUR_010</t>
+  </si>
+  <si>
+    <t>elc_won_TUR_011</t>
+  </si>
+  <si>
+    <t>elc_won_TUR_012</t>
+  </si>
+  <si>
+    <t>elc_won_TUR_002</t>
+  </si>
+  <si>
+    <t>elc_won_TUR_004</t>
+  </si>
+  <si>
+    <t>elc_won_TUR_017</t>
+  </si>
+  <si>
+    <t>elc_won_TUR_023</t>
   </si>
   <si>
     <t>elc_won_TUR_005</t>
@@ -1322,18 +1349,33 @@
     <t>elc_won_TUR_027</t>
   </si>
   <si>
+    <t>elc_won_TUR_008</t>
+  </si>
+  <si>
+    <t>elc_won_TUR_014</t>
+  </si>
+  <si>
     <t>elc_won_TUR_009</t>
   </si>
   <si>
+    <t>elc_won_TUR_024</t>
+  </si>
+  <si>
+    <t>elc_won_TUR_021</t>
+  </si>
+  <si>
+    <t>elc_won_TUR_007</t>
+  </si>
+  <si>
+    <t>elc_won_TUR_013</t>
+  </si>
+  <si>
+    <t>elc_won_TUR_016</t>
+  </si>
+  <si>
     <t>elc_won_TUR_025</t>
   </si>
   <si>
-    <t>elc_won_TUR_008</t>
-  </si>
-  <si>
-    <t>elc_won_TUR_014</t>
-  </si>
-  <si>
     <t>elc_won_TUR_015</t>
   </si>
   <si>
@@ -1343,57 +1385,69 @@
     <t>elc_won_TUR_019</t>
   </si>
   <si>
-    <t>elc_won_TUR_001</t>
-  </si>
-  <si>
-    <t>elc_won_TUR_003</t>
-  </si>
-  <si>
-    <t>elc_won_TUR_010</t>
-  </si>
-  <si>
-    <t>elc_won_TUR_011</t>
-  </si>
-  <si>
-    <t>elc_won_TUR_012</t>
-  </si>
-  <si>
-    <t>elc_won_TUR_013</t>
-  </si>
-  <si>
-    <t>elc_won_TUR_016</t>
-  </si>
-  <si>
-    <t>elc_won_TUR_021</t>
-  </si>
-  <si>
-    <t>elc_won_TUR_024</t>
-  </si>
-  <si>
     <t>elc_won_TUR_020</t>
   </si>
   <si>
-    <t>elc_won_TUR_007</t>
-  </si>
-  <si>
-    <t>elc_won_TUR_002</t>
-  </si>
-  <si>
-    <t>elc_won_TUR_004</t>
-  </si>
-  <si>
-    <t>elc_won_TUR_017</t>
-  </si>
-  <si>
-    <t>elc_won_TUR_023</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_TUR_012</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 12</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_TUR_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_TUR_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_TUR_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_TUR_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_TUR_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_TUR_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_TUR_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_TUR_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_TUR_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_TUR_006</t>
   </si>
   <si>
@@ -1406,28 +1460,16 @@
     <t>connecting wind offshore to buses in cluster 10</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_TUR_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_TUR_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_TUR_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_TUR_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
+    <t>distr_wofelc_wof_TUR_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_TUR_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
   </si>
   <si>
     <t>distr_wofelc_wof_TUR_002</t>
@@ -1436,91 +1478,49 @@
     <t>connecting wind offshore to buses in cluster 2</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_TUR_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_TUR_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_TUR_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_TUR_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_TUR_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_TUR_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_TUR_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
     <t>elc_wof_TUR_012</t>
   </si>
   <si>
+    <t>elc_wof_TUR_004</t>
+  </si>
+  <si>
+    <t>elc_wof_TUR_009</t>
+  </si>
+  <si>
+    <t>elc_wof_TUR_003</t>
+  </si>
+  <si>
+    <t>elc_wof_TUR_011</t>
+  </si>
+  <si>
+    <t>elc_wof_TUR_001</t>
+  </si>
+  <si>
+    <t>elc_wof_TUR_015</t>
+  </si>
+  <si>
+    <t>elc_wof_TUR_005</t>
+  </si>
+  <si>
+    <t>elc_wof_TUR_008</t>
+  </si>
+  <si>
+    <t>elc_wof_TUR_013</t>
+  </si>
+  <si>
     <t>elc_wof_TUR_006</t>
   </si>
   <si>
     <t>elc_wof_TUR_010</t>
   </si>
   <si>
-    <t>elc_wof_TUR_015</t>
-  </si>
-  <si>
-    <t>elc_wof_TUR_004</t>
-  </si>
-  <si>
-    <t>elc_wof_TUR_009</t>
-  </si>
-  <si>
-    <t>elc_wof_TUR_001</t>
+    <t>elc_wof_TUR_007</t>
+  </si>
+  <si>
+    <t>elc_wof_TUR_014</t>
   </si>
   <si>
     <t>elc_wof_TUR_002</t>
-  </si>
-  <si>
-    <t>elc_wof_TUR_005</t>
-  </si>
-  <si>
-    <t>elc_wof_TUR_008</t>
-  </si>
-  <si>
-    <t>elc_wof_TUR_013</t>
-  </si>
-  <si>
-    <t>elc_wof_TUR_003</t>
-  </si>
-  <si>
-    <t>elc_wof_TUR_011</t>
-  </si>
-  <si>
-    <t>elc_wof_TUR_007</t>
-  </si>
-  <si>
-    <t>elc_wof_TUR_014</t>
   </si>
   <si>
     <t>e_won_TUR_001</t>
@@ -5519,7 +5519,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D128763E-A71A-4156-A1E1-25B6E2F79DCC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{407615A9-D21C-4078-B5C8-2BC62226C197}">
   <dimension ref="B9:BD44"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -5757,16 +5757,16 @@
         <v>257</v>
       </c>
       <c r="Y11" t="s">
-        <v>226</v>
+        <v>246</v>
       </c>
       <c r="Z11" t="s">
         <v>329</v>
       </c>
       <c r="AA11">
-        <v>0.99412633551934937</v>
+        <v>0.993933914261249</v>
       </c>
       <c r="AB11">
-        <v>107.68384881192806</v>
+        <v>111.21157187710099</v>
       </c>
       <c r="AD11" t="s">
         <v>256</v>
@@ -5796,13 +5796,13 @@
         <v>414</v>
       </c>
       <c r="AN11" t="s">
-        <v>329</v>
+        <v>346</v>
       </c>
       <c r="AO11">
-        <v>0.99362764803899328</v>
+        <v>0.997920694389545</v>
       </c>
       <c r="AP11">
-        <v>116.82645261845734</v>
+        <v>38.120602858341556</v>
       </c>
       <c r="AR11" t="s">
         <v>256</v>
@@ -5832,7 +5832,7 @@
         <v>471</v>
       </c>
       <c r="BB11" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="BC11">
         <v>0.9934108732525242</v>
@@ -5903,16 +5903,16 @@
         <v>261</v>
       </c>
       <c r="Y12" t="s">
-        <v>227</v>
+        <v>254</v>
       </c>
       <c r="Z12" t="s">
         <v>330</v>
       </c>
       <c r="AA12">
-        <v>0.99619728193378243</v>
+        <v>0.99609734913161818</v>
       </c>
       <c r="AB12">
-        <v>69.716497880655979</v>
+        <v>71.548599253666566</v>
       </c>
       <c r="AD12" t="s">
         <v>256</v>
@@ -5942,13 +5942,13 @@
         <v>415</v>
       </c>
       <c r="AN12" t="s">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="AO12">
-        <v>0.99655204950553855</v>
+        <v>0.99619215494492963</v>
       </c>
       <c r="AP12">
-        <v>63.212425731794113</v>
+        <v>69.810492676290195</v>
       </c>
       <c r="AR12" t="s">
         <v>256</v>
@@ -5978,13 +5978,13 @@
         <v>472</v>
       </c>
       <c r="BB12" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="BC12">
-        <v>0.98612213281971917</v>
+        <v>0.98888864979197166</v>
       </c>
       <c r="BD12">
-        <v>913.67868181308791</v>
+        <v>879.97328336781186</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -6049,16 +6049,16 @@
         <v>263</v>
       </c>
       <c r="Y13" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Z13" t="s">
         <v>331</v>
       </c>
       <c r="AA13">
-        <v>0.99443089844325683</v>
+        <v>0.9932948004327955</v>
       </c>
       <c r="AB13">
-        <v>102.10019520695745</v>
+        <v>122.92865873208331</v>
       </c>
       <c r="AD13" t="s">
         <v>256</v>
@@ -6088,13 +6088,13 @@
         <v>416</v>
       </c>
       <c r="AN13" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="AO13">
-        <v>0.99256313190359724</v>
+        <v>0.99287705863395659</v>
       </c>
       <c r="AP13">
-        <v>136.34258176738365</v>
+        <v>130.58725837746286</v>
       </c>
       <c r="AR13" t="s">
         <v>256</v>
@@ -6124,13 +6124,13 @@
         <v>473</v>
       </c>
       <c r="BB13" t="s">
-        <v>352</v>
+        <v>329</v>
       </c>
       <c r="BC13">
-        <v>0.9944966417365978</v>
+        <v>0.98632698528759588</v>
       </c>
       <c r="BD13">
-        <v>602.57980445059388</v>
+        <v>911.18289591279074</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -6195,16 +6195,16 @@
         <v>265</v>
       </c>
       <c r="Y14" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="Z14" t="s">
         <v>332</v>
       </c>
       <c r="AA14">
-        <v>0.99412800768990783</v>
+        <v>0.99602001668259899</v>
       </c>
       <c r="AB14">
-        <v>107.65319235169031</v>
+        <v>72.966360819018021</v>
       </c>
       <c r="AD14" t="s">
         <v>256</v>
@@ -6234,13 +6234,13 @@
         <v>417</v>
       </c>
       <c r="AN14" t="s">
-        <v>356</v>
+        <v>338</v>
       </c>
       <c r="AO14">
-        <v>0.99509696017521498</v>
+        <v>0.99282493975837693</v>
       </c>
       <c r="AP14">
-        <v>89.889063454392215</v>
+        <v>131.54277109642209</v>
       </c>
       <c r="AR14" t="s">
         <v>256</v>
@@ -6270,13 +6270,13 @@
         <v>474</v>
       </c>
       <c r="BB14" t="s">
-        <v>334</v>
+        <v>353</v>
       </c>
       <c r="BC14">
-        <v>0.98992104174786411</v>
+        <v>0.99356746229949811</v>
       </c>
       <c r="BD14">
-        <v>867.39530803852199</v>
+        <v>661.55172605852022</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -6341,16 +6341,16 @@
         <v>267</v>
       </c>
       <c r="Y15" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="Z15" t="s">
         <v>333</v>
       </c>
       <c r="AA15">
-        <v>0.993933914261249</v>
+        <v>0.99338493407392847</v>
       </c>
       <c r="AB15">
-        <v>111.21157187710099</v>
+        <v>121.27620864464539</v>
       </c>
       <c r="AD15" t="s">
         <v>256</v>
@@ -6380,13 +6380,13 @@
         <v>418</v>
       </c>
       <c r="AN15" t="s">
-        <v>334</v>
+        <v>359</v>
       </c>
       <c r="AO15">
-        <v>0.99633464844626451</v>
+        <v>0.99428674451774723</v>
       </c>
       <c r="AP15">
-        <v>67.198111818484705</v>
+        <v>104.74301717463503</v>
       </c>
       <c r="AR15" t="s">
         <v>256</v>
@@ -6419,10 +6419,10 @@
         <v>335</v>
       </c>
       <c r="BC15">
-        <v>0.98888864979197166</v>
+        <v>0.99073521642138018</v>
       </c>
       <c r="BD15">
-        <v>879.97328336781186</v>
+        <v>841.30493112307329</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -6487,16 +6487,16 @@
         <v>269</v>
       </c>
       <c r="Y16" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="Z16" t="s">
         <v>334</v>
       </c>
       <c r="AA16">
-        <v>0.99609734913161818</v>
+        <v>0.99691024577718534</v>
       </c>
       <c r="AB16">
-        <v>71.548599253666566</v>
+        <v>56.645494084936288</v>
       </c>
       <c r="AD16" t="s">
         <v>256</v>
@@ -6526,13 +6526,13 @@
         <v>419</v>
       </c>
       <c r="AN16" t="s">
-        <v>335</v>
+        <v>351</v>
       </c>
       <c r="AO16">
-        <v>0.99289722117962842</v>
+        <v>0.99657584845749059</v>
       </c>
       <c r="AP16">
-        <v>130.21761170681245</v>
+        <v>62.776111612673049</v>
       </c>
       <c r="AR16" t="s">
         <v>256</v>
@@ -6562,13 +6562,13 @@
         <v>476</v>
       </c>
       <c r="BB16" t="s">
-        <v>333</v>
+        <v>351</v>
       </c>
       <c r="BC16">
-        <v>0.98632698528759588</v>
+        <v>0.99324346587677392</v>
       </c>
       <c r="BD16">
-        <v>911.18289591279074</v>
+        <v>682.11469902074725</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -6633,16 +6633,16 @@
         <v>271</v>
       </c>
       <c r="Y17" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="Z17" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="AA17">
-        <v>0.99530666643476395</v>
+        <v>0.99295282620806036</v>
       </c>
       <c r="AB17">
-        <v>86.044448695994831</v>
+        <v>129.19818618555928</v>
       </c>
       <c r="AD17" t="s">
         <v>256</v>
@@ -6672,13 +6672,13 @@
         <v>420</v>
       </c>
       <c r="AN17" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="AO17">
-        <v>0.99686336779372176</v>
+        <v>0.99519354197412024</v>
       </c>
       <c r="AP17">
-        <v>57.504923781768397</v>
+        <v>88.118397141128597</v>
       </c>
       <c r="AR17" t="s">
         <v>256</v>
@@ -6708,13 +6708,13 @@
         <v>477</v>
       </c>
       <c r="BB17" t="s">
-        <v>349</v>
+        <v>330</v>
       </c>
       <c r="BC17">
-        <v>0.99324346587677392</v>
+        <v>0.98992104174786411</v>
       </c>
       <c r="BD17">
-        <v>682.11469902074725</v>
+        <v>867.39530803852199</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -6779,16 +6779,16 @@
         <v>273</v>
       </c>
       <c r="Y18" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="Z18" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AA18">
-        <v>0.99378697710364916</v>
+        <v>0.994772031603258</v>
       </c>
       <c r="AB18">
-        <v>113.90541976643259</v>
+        <v>95.846087273602649</v>
       </c>
       <c r="AD18" t="s">
         <v>256</v>
@@ -6818,13 +6818,13 @@
         <v>421</v>
       </c>
       <c r="AN18" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="AO18">
-        <v>0.99674051815630915</v>
+        <v>0.99404969682668387</v>
       </c>
       <c r="AP18">
-        <v>59.757167134333223</v>
+        <v>109.08889151079572</v>
       </c>
       <c r="AR18" t="s">
         <v>256</v>
@@ -6854,13 +6854,13 @@
         <v>478</v>
       </c>
       <c r="BB18" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="BC18">
-        <v>0.99531868162568826</v>
+        <v>0.9861337214127881</v>
       </c>
       <c r="BD18">
-        <v>550.40767282298157</v>
+        <v>913.53749412086438</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -6925,16 +6925,16 @@
         <v>275</v>
       </c>
       <c r="Y19" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="Z19" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AA19">
-        <v>0.99500934522815321</v>
+        <v>0.99711350851742464</v>
       </c>
       <c r="AB19">
-        <v>91.495337483857028</v>
+        <v>52.91901051388075</v>
       </c>
       <c r="AD19" t="s">
         <v>256</v>
@@ -6964,13 +6964,13 @@
         <v>422</v>
       </c>
       <c r="AN19" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="AO19">
-        <v>0.99310515301754987</v>
+        <v>0.99836222355563642</v>
       </c>
       <c r="AP19">
-        <v>126.40552801158564</v>
+        <v>30.025901479999618</v>
       </c>
       <c r="AR19" t="s">
         <v>256</v>
@@ -7000,13 +7000,13 @@
         <v>479</v>
       </c>
       <c r="BB19" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="BC19">
-        <v>0.9861337214127881</v>
+        <v>0.98878264935664117</v>
       </c>
       <c r="BD19">
-        <v>913.53749412086438</v>
+        <v>881.26472200492208</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -7071,16 +7071,16 @@
         <v>277</v>
       </c>
       <c r="Y20" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="Z20" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AA20">
-        <v>0.994772031603258</v>
+        <v>0.99513284024630766</v>
       </c>
       <c r="AB20">
-        <v>95.846087273602649</v>
+        <v>89.231262151026939</v>
       </c>
       <c r="AD20" t="s">
         <v>256</v>
@@ -7110,13 +7110,13 @@
         <v>423</v>
       </c>
       <c r="AN20" t="s">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="AO20">
-        <v>0.99769569039591344</v>
+        <v>0.99362764803899328</v>
       </c>
       <c r="AP20">
-        <v>42.245676074919672</v>
+        <v>116.82645261845734</v>
       </c>
       <c r="AR20" t="s">
         <v>256</v>
@@ -7146,13 +7146,13 @@
         <v>480</v>
       </c>
       <c r="BB20" t="s">
-        <v>358</v>
+        <v>337</v>
       </c>
       <c r="BC20">
-        <v>0.98878264935664117</v>
+        <v>0.99663885821479647</v>
       </c>
       <c r="BD20">
-        <v>881.26472200492208</v>
+        <v>466.62046530091408</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -7217,16 +7217,16 @@
         <v>279</v>
       </c>
       <c r="Y21" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="Z21" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AA21">
-        <v>0.99711350851742464</v>
+        <v>0.99407707520632382</v>
       </c>
       <c r="AB21">
-        <v>52.91901051388075</v>
+        <v>108.5869545507289</v>
       </c>
       <c r="AD21" t="s">
         <v>256</v>
@@ -7256,13 +7256,13 @@
         <v>424</v>
       </c>
       <c r="AN21" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="AO21">
-        <v>0.99435363045737235</v>
+        <v>0.99655204950553855</v>
       </c>
       <c r="AP21">
-        <v>103.51677494817308</v>
+        <v>63.212425731794113</v>
       </c>
       <c r="AR21" t="s">
         <v>256</v>
@@ -7295,10 +7295,10 @@
         <v>338</v>
       </c>
       <c r="BC21">
-        <v>0.99663885821479647</v>
+        <v>0.98612213281971917</v>
       </c>
       <c r="BD21">
-        <v>466.62046530091408</v>
+        <v>913.67868181308791</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -7363,16 +7363,16 @@
         <v>281</v>
       </c>
       <c r="Y22" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="Z22" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AA22">
-        <v>0.9947827831753886</v>
+        <v>0.99311250392571082</v>
       </c>
       <c r="AB22">
-        <v>95.648975117876532</v>
+        <v>126.27076136196735</v>
       </c>
       <c r="AD22" t="s">
         <v>256</v>
@@ -7402,13 +7402,13 @@
         <v>425</v>
       </c>
       <c r="AN22" t="s">
-        <v>333</v>
+        <v>355</v>
       </c>
       <c r="AO22">
-        <v>0.98839089880478714</v>
+        <v>0.99256313190359724</v>
       </c>
       <c r="AP22">
-        <v>212.83352191223577</v>
+        <v>136.34258176738365</v>
       </c>
       <c r="AR22" t="s">
         <v>256</v>
@@ -7438,13 +7438,13 @@
         <v>482</v>
       </c>
       <c r="BB22" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="BC22">
-        <v>0.99356746229949811</v>
+        <v>0.9944966417365978</v>
       </c>
       <c r="BD22">
-        <v>661.55172605852022</v>
+        <v>602.57980445059388</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -7509,16 +7509,16 @@
         <v>283</v>
       </c>
       <c r="Y23" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="Z23" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AA23">
-        <v>0.99796206558644474</v>
+        <v>0.99530666643476395</v>
       </c>
       <c r="AB23">
-        <v>37.362130915179783</v>
+        <v>86.044448695994831</v>
       </c>
       <c r="AD23" t="s">
         <v>256</v>
@@ -7548,13 +7548,13 @@
         <v>426</v>
       </c>
       <c r="AN23" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="AO23">
-        <v>0.997920694389545</v>
+        <v>0.99509696017521498</v>
       </c>
       <c r="AP23">
-        <v>38.120602858341556</v>
+        <v>89.889063454392215</v>
       </c>
       <c r="AR23" t="s">
         <v>256</v>
@@ -7584,13 +7584,13 @@
         <v>483</v>
       </c>
       <c r="BB23" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="BC23">
-        <v>0.99073521642138018</v>
+        <v>0.99565502951366147</v>
       </c>
       <c r="BD23">
-        <v>841.30493112307329</v>
+        <v>529.06079353295013</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -7655,16 +7655,16 @@
         <v>285</v>
       </c>
       <c r="Y24" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="Z24" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AA24">
-        <v>0.99377039019010449</v>
+        <v>0.99378697710364916</v>
       </c>
       <c r="AB24">
-        <v>114.2095131814169</v>
+        <v>113.90541976643259</v>
       </c>
       <c r="AD24" t="s">
         <v>256</v>
@@ -7694,13 +7694,13 @@
         <v>427</v>
       </c>
       <c r="AN24" t="s">
-        <v>351</v>
+        <v>330</v>
       </c>
       <c r="AO24">
-        <v>0.99619215494492963</v>
+        <v>0.99633464844626451</v>
       </c>
       <c r="AP24">
-        <v>69.810492676290195</v>
+        <v>67.198111818484705</v>
       </c>
       <c r="AR24" t="s">
         <v>256</v>
@@ -7730,13 +7730,13 @@
         <v>484</v>
       </c>
       <c r="BB24" t="s">
-        <v>339</v>
+        <v>358</v>
       </c>
       <c r="BC24">
-        <v>0.99565502951366147</v>
+        <v>0.99548747628591994</v>
       </c>
       <c r="BD24">
-        <v>529.06079353295013</v>
+        <v>539.69483838694953</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -7801,16 +7801,16 @@
         <v>287</v>
       </c>
       <c r="Y25" t="s">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="Z25" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AA25">
-        <v>0.99678417683109988</v>
+        <v>0.99500934522815321</v>
       </c>
       <c r="AB25">
-        <v>58.956758096501645</v>
+        <v>91.495337483857028</v>
       </c>
       <c r="AD25" t="s">
         <v>256</v>
@@ -7840,13 +7840,13 @@
         <v>428</v>
       </c>
       <c r="AN25" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="AO25">
-        <v>0.99287705863395659</v>
+        <v>0.99674051815630915</v>
       </c>
       <c r="AP25">
-        <v>130.58725837746286</v>
+        <v>59.757167134333223</v>
       </c>
       <c r="AR25" t="s">
         <v>256</v>
@@ -7876,13 +7876,13 @@
         <v>485</v>
       </c>
       <c r="BB25" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="BC25">
-        <v>0.99548747628591994</v>
+        <v>0.99531868162568826</v>
       </c>
       <c r="BD25">
-        <v>539.69483838694953</v>
+        <v>550.40767282298157</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -7947,16 +7947,16 @@
         <v>289</v>
       </c>
       <c r="Y26" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="Z26" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AA26">
-        <v>0.9932948004327955</v>
+        <v>0.99553748992442859</v>
       </c>
       <c r="AB26">
-        <v>122.92865873208331</v>
+        <v>81.812684718809606</v>
       </c>
       <c r="AD26" t="s">
         <v>256</v>
@@ -7986,13 +7986,13 @@
         <v>429</v>
       </c>
       <c r="AN26" t="s">
-        <v>357</v>
+        <v>332</v>
       </c>
       <c r="AO26">
-        <v>0.99282493975837693</v>
+        <v>0.99310515301754987</v>
       </c>
       <c r="AP26">
-        <v>131.54277109642209</v>
+        <v>126.40552801158564</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -8057,16 +8057,16 @@
         <v>291</v>
       </c>
       <c r="Y27" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="Z27" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AA27">
-        <v>0.99602001668259899</v>
+        <v>0.99339395914723061</v>
       </c>
       <c r="AB27">
-        <v>72.966360819018021</v>
+        <v>121.11074896743884</v>
       </c>
       <c r="AD27" t="s">
         <v>256</v>
@@ -8096,13 +8096,13 @@
         <v>430</v>
       </c>
       <c r="AN27" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="AO27">
-        <v>0.99428674451774723</v>
+        <v>0.99289722117962842</v>
       </c>
       <c r="AP27">
-        <v>104.74301717463503</v>
+        <v>130.21761170681245</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -8167,16 +8167,16 @@
         <v>293</v>
       </c>
       <c r="Y28" t="s">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="Z28" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AA28">
-        <v>0.99338493407392847</v>
+        <v>0.99371077029882426</v>
       </c>
       <c r="AB28">
-        <v>121.27620864464539</v>
+        <v>115.30254452155468</v>
       </c>
       <c r="AD28" t="s">
         <v>256</v>
@@ -8206,13 +8206,13 @@
         <v>431</v>
       </c>
       <c r="AN28" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="AO28">
-        <v>0.99343963324503992</v>
+        <v>0.99849244413689819</v>
       </c>
       <c r="AP28">
-        <v>120.2733905076018</v>
+        <v>27.638524156865536</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -8277,16 +8277,16 @@
         <v>295</v>
       </c>
       <c r="Y29" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="Z29" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AA29">
-        <v>0.99691024577718534</v>
+        <v>0.99796206558644474</v>
       </c>
       <c r="AB29">
-        <v>56.645494084936288</v>
+        <v>37.362130915179783</v>
       </c>
       <c r="AD29" t="s">
         <v>256</v>
@@ -8316,13 +8316,13 @@
         <v>432</v>
       </c>
       <c r="AN29" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="AO29">
-        <v>0.9938793658002224</v>
+        <v>0.99167334417469333</v>
       </c>
       <c r="AP29">
-        <v>112.21162699592226</v>
+        <v>152.65535679728958</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -8387,16 +8387,16 @@
         <v>297</v>
       </c>
       <c r="Y30" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="Z30" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AA30">
-        <v>0.99295282620806036</v>
+        <v>0.99377039019010449</v>
       </c>
       <c r="AB30">
-        <v>129.19818618555928</v>
+        <v>114.2095131814169</v>
       </c>
       <c r="AD30" t="s">
         <v>256</v>
@@ -8426,13 +8426,13 @@
         <v>433</v>
       </c>
       <c r="AN30" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="AO30">
-        <v>0.99167334417469333</v>
+        <v>0.99537645627164983</v>
       </c>
       <c r="AP30">
-        <v>152.65535679728958</v>
+        <v>84.764968353085692</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -8500,7 +8500,7 @@
         <v>224</v>
       </c>
       <c r="Z31" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AA31">
         <v>0.99317173858248919</v>
@@ -8536,13 +8536,13 @@
         <v>434</v>
       </c>
       <c r="AN31" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="AO31">
-        <v>0.99849244413689819</v>
+        <v>0.99343963324503992</v>
       </c>
       <c r="AP31">
-        <v>27.638524156865536</v>
+        <v>120.2733905076018</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -8607,16 +8607,16 @@
         <v>301</v>
       </c>
       <c r="Y32" t="s">
-        <v>222</v>
+        <v>253</v>
       </c>
       <c r="Z32" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AA32">
-        <v>0.99641837849962689</v>
+        <v>0.99601912084206656</v>
       </c>
       <c r="AB32">
-        <v>65.663060840172875</v>
+        <v>72.982784562113636</v>
       </c>
       <c r="AD32" t="s">
         <v>256</v>
@@ -8646,13 +8646,13 @@
         <v>435</v>
       </c>
       <c r="AN32" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="AO32">
-        <v>0.9940371535287178</v>
+        <v>0.9938793658002224</v>
       </c>
       <c r="AP32">
-        <v>109.3188519735061</v>
+        <v>112.21162699592226</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -8717,16 +8717,16 @@
         <v>303</v>
       </c>
       <c r="Y33" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
       <c r="Z33" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="AA33">
-        <v>0.99317596161262944</v>
+        <v>0.99641837849962689</v>
       </c>
       <c r="AB33">
-        <v>125.10737043512741</v>
+        <v>65.663060840172875</v>
       </c>
       <c r="AD33" t="s">
         <v>256</v>
@@ -8756,13 +8756,13 @@
         <v>436</v>
       </c>
       <c r="AN33" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="AO33">
-        <v>0.99537645627164983</v>
+        <v>0.99686336779372176</v>
       </c>
       <c r="AP33">
-        <v>84.764968353085692</v>
+        <v>57.504923781768397</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -8827,16 +8827,16 @@
         <v>305</v>
       </c>
       <c r="Y34" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="Z34" t="s">
-        <v>350</v>
+        <v>334</v>
       </c>
       <c r="AA34">
-        <v>0.99598440277473888</v>
+        <v>0.99317596161262944</v>
       </c>
       <c r="AB34">
-        <v>73.619282463120172</v>
+        <v>125.10737043512741</v>
       </c>
       <c r="AD34" t="s">
         <v>256</v>
@@ -8866,13 +8866,13 @@
         <v>437</v>
       </c>
       <c r="AN34" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="AO34">
-        <v>0.99657584845749059</v>
+        <v>0.99769569039591344</v>
       </c>
       <c r="AP34">
-        <v>62.776111612673049</v>
+        <v>42.245676074919672</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -8937,16 +8937,16 @@
         <v>307</v>
       </c>
       <c r="Y35" t="s">
-        <v>223</v>
+        <v>250</v>
       </c>
       <c r="Z35" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AA35">
-        <v>0.99553748992442859</v>
+        <v>0.99598440277473888</v>
       </c>
       <c r="AB35">
-        <v>81.812684718809606</v>
+        <v>73.619282463120172</v>
       </c>
       <c r="AD35" t="s">
         <v>256</v>
@@ -8976,13 +8976,13 @@
         <v>438</v>
       </c>
       <c r="AN35" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="AO35">
-        <v>0.99519354197412024</v>
+        <v>0.99435363045737235</v>
       </c>
       <c r="AP35">
-        <v>88.118397141128597</v>
+        <v>103.51677494817308</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -9047,16 +9047,16 @@
         <v>309</v>
       </c>
       <c r="Y36" t="s">
-        <v>247</v>
+        <v>226</v>
       </c>
       <c r="Z36" t="s">
-        <v>352</v>
+        <v>341</v>
       </c>
       <c r="AA36">
-        <v>0.99339395914723061</v>
+        <v>0.99412633551934937</v>
       </c>
       <c r="AB36">
-        <v>121.11074896743884</v>
+        <v>107.68384881192806</v>
       </c>
       <c r="AD36" t="s">
         <v>256</v>
@@ -9086,13 +9086,13 @@
         <v>439</v>
       </c>
       <c r="AN36" t="s">
-        <v>346</v>
+        <v>329</v>
       </c>
       <c r="AO36">
-        <v>0.99404969682668387</v>
+        <v>0.98839089880478714</v>
       </c>
       <c r="AP36">
-        <v>109.08889151079572</v>
+        <v>212.83352191223577</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -9157,16 +9157,16 @@
         <v>311</v>
       </c>
       <c r="Y37" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="Z37" t="s">
         <v>353</v>
       </c>
       <c r="AA37">
-        <v>0.99371077029882426</v>
+        <v>0.99619728193378243</v>
       </c>
       <c r="AB37">
-        <v>115.30254452155468</v>
+        <v>69.716497880655979</v>
       </c>
       <c r="AD37" t="s">
         <v>256</v>
@@ -9196,13 +9196,13 @@
         <v>440</v>
       </c>
       <c r="AN37" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="AO37">
-        <v>0.99836222355563642</v>
+        <v>0.9940371535287178</v>
       </c>
       <c r="AP37">
-        <v>30.025901479999618</v>
+        <v>109.3188519735061</v>
       </c>
     </row>
     <row r="38" spans="2:42">
@@ -9267,16 +9267,16 @@
         <v>313</v>
       </c>
       <c r="Y38" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="Z38" t="s">
         <v>354</v>
       </c>
       <c r="AA38">
-        <v>0.9953018867226836</v>
+        <v>0.99443089844325683</v>
       </c>
       <c r="AB38">
-        <v>86.132076750799584</v>
+        <v>102.10019520695745</v>
       </c>
     </row>
     <row r="39" spans="2:42">
@@ -9341,16 +9341,16 @@
         <v>315</v>
       </c>
       <c r="Y39" t="s">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="Z39" t="s">
-        <v>336</v>
+        <v>355</v>
       </c>
       <c r="AA39">
-        <v>0.99227449562090098</v>
+        <v>0.99412800768990783</v>
       </c>
       <c r="AB39">
-        <v>141.63424695014979</v>
+        <v>107.65319235169031</v>
       </c>
     </row>
     <row r="40" spans="2:42">
@@ -9415,16 +9415,16 @@
         <v>317</v>
       </c>
       <c r="Y40" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="Z40" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AA40">
-        <v>0.99598117863855251</v>
+        <v>0.9953018867226836</v>
       </c>
       <c r="AB40">
-        <v>73.678391626536893</v>
+        <v>86.132076750799584</v>
       </c>
     </row>
     <row r="41" spans="2:42">
@@ -9489,16 +9489,16 @@
         <v>319</v>
       </c>
       <c r="Y41" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="Z41" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="AA41">
-        <v>0.99601912084206656</v>
+        <v>0.99227449562090098</v>
       </c>
       <c r="AB41">
-        <v>72.982784562113636</v>
+        <v>141.63424695014979</v>
       </c>
     </row>
     <row r="42" spans="2:42">
@@ -9563,16 +9563,16 @@
         <v>321</v>
       </c>
       <c r="Y42" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="Z42" t="s">
         <v>357</v>
       </c>
       <c r="AA42">
-        <v>0.99513284024630766</v>
+        <v>0.99598117863855251</v>
       </c>
       <c r="AB42">
-        <v>89.231262151026939</v>
+        <v>73.678391626536893</v>
       </c>
     </row>
     <row r="43" spans="2:42">
@@ -9637,16 +9637,16 @@
         <v>323</v>
       </c>
       <c r="Y43" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="Z43" t="s">
         <v>358</v>
       </c>
       <c r="AA43">
-        <v>0.99407707520632382</v>
+        <v>0.99678417683109988</v>
       </c>
       <c r="AB43">
-        <v>108.5869545507289</v>
+        <v>58.956758096501645</v>
       </c>
     </row>
     <row r="44" spans="2:42">
@@ -9711,16 +9711,16 @@
         <v>325</v>
       </c>
       <c r="Y44" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="Z44" t="s">
         <v>359</v>
       </c>
       <c r="AA44">
-        <v>0.99311250392571082</v>
+        <v>0.9947827831753886</v>
       </c>
       <c r="AB44">
-        <v>126.27076136196735</v>
+        <v>95.648975117876532</v>
       </c>
     </row>
   </sheetData>
@@ -9729,7 +9729,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA2E5925-FAA4-437C-AFF9-9BE12E7930F2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC36108D-4E31-4095-A3B8-C3BEA576D0C6}">
   <dimension ref="B9:Z37"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9841,7 +9841,7 @@
         <v>486</v>
       </c>
       <c r="K11" t="s">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -9874,7 +9874,7 @@
         <v>540</v>
       </c>
       <c r="X11" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="Y11">
         <v>28.41225</v>
@@ -9909,7 +9909,7 @@
         <v>488</v>
       </c>
       <c r="K12" t="s">
-        <v>437</v>
+        <v>419</v>
       </c>
       <c r="L12">
         <v>0.47087349200844925</v>
@@ -9942,7 +9942,7 @@
         <v>542</v>
       </c>
       <c r="X12" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="Y12">
         <v>1.161</v>
@@ -9977,7 +9977,7 @@
         <v>490</v>
       </c>
       <c r="K13" t="s">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="L13">
         <v>1.112348760609714</v>
@@ -10010,7 +10010,7 @@
         <v>544</v>
       </c>
       <c r="X13" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="Y13">
         <v>25.173749999999998</v>
@@ -10045,7 +10045,7 @@
         <v>492</v>
       </c>
       <c r="K14" t="s">
-        <v>438</v>
+        <v>420</v>
       </c>
       <c r="L14">
         <v>5.1692791401678786</v>
@@ -10078,7 +10078,7 @@
         <v>546</v>
       </c>
       <c r="X14" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="Y14">
         <v>12.55725</v>
@@ -10113,7 +10113,7 @@
         <v>494</v>
       </c>
       <c r="K15" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="L15">
         <v>3.5713534804806977</v>
@@ -10146,7 +10146,7 @@
         <v>548</v>
       </c>
       <c r="X15" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="Y15">
         <v>3.4432499999999999</v>
@@ -10181,7 +10181,7 @@
         <v>496</v>
       </c>
       <c r="K16" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="L16">
         <v>1.1361468497474501</v>
@@ -10214,7 +10214,7 @@
         <v>550</v>
       </c>
       <c r="X16" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="Y16">
         <v>0.50249999999999995</v>
@@ -10249,7 +10249,7 @@
         <v>498</v>
       </c>
       <c r="K17" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="L17">
         <v>3.0196919643694575</v>
@@ -10282,7 +10282,7 @@
         <v>552</v>
       </c>
       <c r="X17" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="Y17">
         <v>17.266500000000001</v>
@@ -10317,7 +10317,7 @@
         <v>500</v>
       </c>
       <c r="K18" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="L18">
         <v>1.4503821392266858E-2</v>
@@ -10350,7 +10350,7 @@
         <v>554</v>
       </c>
       <c r="X18" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="Y18">
         <v>14.892749999999999</v>
@@ -10385,7 +10385,7 @@
         <v>502</v>
       </c>
       <c r="K19" t="s">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="L19">
         <v>5.0823754535521983</v>
@@ -10418,7 +10418,7 @@
         <v>556</v>
       </c>
       <c r="X19" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="Y19">
         <v>7.9275000000000002</v>
@@ -10453,7 +10453,7 @@
         <v>504</v>
       </c>
       <c r="K20" t="s">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="L20">
         <v>8.514044986304631</v>
@@ -10486,7 +10486,7 @@
         <v>558</v>
       </c>
       <c r="X20" t="s">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="Y20">
         <v>20.379000000000001</v>
@@ -10521,7 +10521,7 @@
         <v>506</v>
       </c>
       <c r="K21" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="L21">
         <v>1.1170819926179429</v>
@@ -10554,7 +10554,7 @@
         <v>560</v>
       </c>
       <c r="X21" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="Y21">
         <v>8.5830000000000002</v>
@@ -10589,7 +10589,7 @@
         <v>508</v>
       </c>
       <c r="K22" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="L22">
         <v>0.50905699240135649</v>
@@ -10657,7 +10657,7 @@
         <v>510</v>
       </c>
       <c r="K23" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="L23">
         <v>1.7273188195461551</v>
@@ -10690,7 +10690,7 @@
         <v>564</v>
       </c>
       <c r="X23" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="Y23">
         <v>3.3195000000000001</v>
@@ -10725,7 +10725,7 @@
         <v>512</v>
       </c>
       <c r="K24" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="L24">
         <v>0.36717216510020872</v>
@@ -10758,7 +10758,7 @@
         <v>566</v>
       </c>
       <c r="X24" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Y24">
         <v>23.857500000000002</v>
@@ -10793,7 +10793,7 @@
         <v>514</v>
       </c>
       <c r="K25" t="s">
-        <v>423</v>
+        <v>437</v>
       </c>
       <c r="L25">
         <v>0.81573616188815345</v>
@@ -10826,7 +10826,7 @@
         <v>568</v>
       </c>
       <c r="X25" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="Y25">
         <v>0.84450000000000003</v>
@@ -10861,7 +10861,7 @@
         <v>516</v>
       </c>
       <c r="K26" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="L26">
         <v>2.4219190334572569</v>
@@ -10896,7 +10896,7 @@
         <v>518</v>
       </c>
       <c r="K27" t="s">
-        <v>439</v>
+        <v>421</v>
       </c>
       <c r="L27">
         <v>3.9442935606378553</v>
@@ -10931,7 +10931,7 @@
         <v>520</v>
       </c>
       <c r="K28" t="s">
-        <v>424</v>
+        <v>438</v>
       </c>
       <c r="L28">
         <v>3.3142885016941812</v>
@@ -10966,7 +10966,7 @@
         <v>522</v>
       </c>
       <c r="K29" t="s">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="L29">
         <v>2.3850731937632021E-2</v>
@@ -11001,7 +11001,7 @@
         <v>524</v>
       </c>
       <c r="K30" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="L30">
         <v>3.6498718196831179</v>
@@ -11036,7 +11036,7 @@
         <v>526</v>
       </c>
       <c r="K31" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="L31">
         <v>0.92563501101913559</v>
@@ -11071,7 +11071,7 @@
         <v>528</v>
       </c>
       <c r="K32" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="L32">
         <v>0.83793427705899637</v>
@@ -11106,7 +11106,7 @@
         <v>530</v>
       </c>
       <c r="K33" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -11141,7 +11141,7 @@
         <v>532</v>
       </c>
       <c r="K34" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -11176,7 +11176,7 @@
         <v>534</v>
       </c>
       <c r="K35" t="s">
-        <v>420</v>
+        <v>436</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -11211,7 +11211,7 @@
         <v>536</v>
       </c>
       <c r="K36" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="L36">
         <v>7.4212893831082968E-2</v>
@@ -11246,7 +11246,7 @@
         <v>538</v>
       </c>
       <c r="K37" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="L37">
         <v>0.34025648567732208</v>
@@ -11261,7 +11261,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{743073E4-54D0-4D5F-BE4B-5968C0209BD5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{241CCD06-C3C4-4A61-8839-0B21B63E099C}">
   <dimension ref="B9:Y151"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
